--- a/sheets/S08A22P241.xlsx
+++ b/sheets/S08A22P241.xlsx
@@ -4678,7 +4678,7 @@
     <t>Maher Singh</t>
   </si>
   <si>
-    <t>Rajबाला</t>
+    <t>Rajbala</t>
   </si>
   <si>
     <t>IOX1405182</t>
